--- a/data/trans_orig/P23_1_2016_2023_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023_R2-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2016</t>
+          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44797</t>
+          <t>43394</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400889</t>
+          <t>400747</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414209</t>
+          <t>414273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>365786</t>
+          <t>363475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>383053</t>
+          <t>382629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>770421</t>
+          <t>771824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>793619</t>
+          <t>793666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>38301</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66511</t>
+          <t>66651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77237</t>
+          <t>75882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94595</t>
+          <t>94188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135623</t>
+          <t>133767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>523985</t>
+          <t>523845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>550883</t>
+          <t>552195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486307</t>
+          <t>487662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515833</t>
+          <t>515694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1018417</t>
+          <t>1020273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1059445</t>
+          <t>1059852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69404</t>
+          <t>69911</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104930</t>
+          <t>105167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81317</t>
+          <t>83822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118800</t>
+          <t>119584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159643</t>
+          <t>161599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214404</t>
+          <t>213216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>563095</t>
+          <t>562858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>598621</t>
+          <t>598114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>541659</t>
+          <t>540875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>579142</t>
+          <t>576637</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1114079</t>
+          <t>1115267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1168840</t>
+          <t>1166884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111072</t>
+          <t>111307</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155131</t>
+          <t>154402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82840</t>
+          <t>82721</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122779</t>
+          <t>120379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204817</t>
+          <t>204517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261649</t>
+          <t>261660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>490917</t>
+          <t>491646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>534976</t>
+          <t>534741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>524182</t>
+          <t>526582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>564121</t>
+          <t>564240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1031360</t>
+          <t>1031349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1088192</t>
+          <t>1088492</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,18%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139555</t>
+          <t>139370</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181454</t>
+          <t>180395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53319</t>
+          <t>53524</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87112</t>
+          <t>87611</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202559</t>
+          <t>199570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>259153</t>
+          <t>257241</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296464</t>
+          <t>297523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338363</t>
+          <t>338548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>408628</t>
+          <t>408129</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442421</t>
+          <t>442216</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>714505</t>
+          <t>716417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>771099</t>
+          <t>774088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124558</t>
+          <t>123679</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>158895</t>
+          <t>159711</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45327</t>
+          <t>45285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>151553</t>
+          <t>151316</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197712</t>
+          <t>196677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175435</t>
+          <t>174619</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209772</t>
+          <t>210651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332435</t>
+          <t>332477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>355454</t>
+          <t>355938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514380</t>
+          <t>515415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>560539</t>
+          <t>560776</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108477</t>
+          <t>108564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136447</t>
+          <t>135746</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>14528</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108366</t>
+          <t>107236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>146352</t>
+          <t>145487</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119686</t>
+          <t>120387</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147656</t>
+          <t>147569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>385843</t>
+          <t>384356</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>397679</t>
+          <t>397667</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>508665</t>
+          <t>509530</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>546651</t>
+          <t>547781</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>657162</t>
+          <t>657993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>752570</t>
+          <t>752729</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>351632</t>
+          <t>351550</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>424406</t>
+          <t>427302</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1034000</t>
+          <t>1025856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1154938</t>
+          <t>1154919</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2639844</t>
+          <t>2639685</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2735252</t>
+          <t>2734421</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3114697</t>
+          <t>3111801</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3187471</t>
+          <t>3187553</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5776579</t>
+          <t>5776598</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5897517</t>
+          <t>5905661</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2023</t>
+          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23759</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32561</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43515</t>
+          <t>44159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376228</t>
+          <t>376115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398175</t>
+          <t>398132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278077</t>
+          <t>279461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300863</t>
+          <t>301265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>667110</t>
+          <t>666466</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>695883</t>
+          <t>695694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>33672</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>45273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33977</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69300</t>
+          <t>70439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389573</t>
+          <t>389875</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411623</t>
+          <t>412463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467028</t>
+          <t>466231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493913</t>
+          <t>493509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>865751</t>
+          <t>864612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>901074</t>
+          <t>899012</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32932</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60409</t>
+          <t>59190</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>41421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63923</t>
+          <t>63772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80141</t>
+          <t>80650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116961</t>
+          <t>119816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>475765</t>
+          <t>476984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>503242</t>
+          <t>504629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>478545</t>
+          <t>478696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>500579</t>
+          <t>501047</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>961680</t>
+          <t>958825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>998500</t>
+          <t>997991</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134779</t>
+          <t>134658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>661235</t>
+          <t>640394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71234</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102406</t>
+          <t>102912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>218083</t>
+          <t>215490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>924638</t>
+          <t>894997</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225548</t>
+          <t>246389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>752004</t>
+          <t>752125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>609131</t>
+          <t>608625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640303</t>
+          <t>640216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>673682</t>
+          <t>703323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1380237</t>
+          <t>1382830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140951</t>
+          <t>138495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181706</t>
+          <t>180474</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75353</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101529</t>
+          <t>98440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220336</t>
+          <t>220115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269672</t>
+          <t>269526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>378498</t>
+          <t>379730</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>419253</t>
+          <t>421709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>446376</t>
+          <t>449465</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>472552</t>
+          <t>474571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>838437</t>
+          <t>838583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>887773</t>
+          <t>887994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>141113</t>
+          <t>140288</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>170654</t>
+          <t>170158</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74442</t>
+          <t>75053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110951</t>
+          <t>102857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>261224</t>
+          <t>263555</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197511</t>
+          <t>198007</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227052</t>
+          <t>227877</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>533926</t>
+          <t>533315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>590499</t>
+          <t>589117</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>715309</t>
+          <t>712978</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>865582</t>
+          <t>873676</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104952</t>
+          <t>104129</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130884</t>
+          <t>130017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24263</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121163</t>
+          <t>119826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153162</t>
+          <t>151806</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>151875</t>
+          <t>152742</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177807</t>
+          <t>178630</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>401568</t>
+          <t>401157</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>413570</t>
+          <t>413498</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>555428</t>
+          <t>556784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>587427</t>
+          <t>588764</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>637003</t>
+          <t>641386</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1404653</t>
+          <t>1477012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>261388</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>376266</t>
+          <t>377059</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>946969</t>
+          <t>950224</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1975074</t>
+          <t>1829952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2052967</t>
+          <t>1980608</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2820617</t>
+          <t>2816234</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3281985</t>
+          <t>3281192</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3396863</t>
+          <t>3382553</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5140797</t>
+          <t>5285919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6168902</t>
+          <t>6165647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_1_2016_2023_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023_R2-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32280</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21552</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43394</t>
+          <t>42759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400747</t>
+          <t>401537</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414273</t>
+          <t>414296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>363475</t>
+          <t>364873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>382629</t>
+          <t>382492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>771824</t>
+          <t>772459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>793666</t>
+          <t>794661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38301</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66651</t>
+          <t>68109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47850</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75882</t>
+          <t>76725</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94188</t>
+          <t>94160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133767</t>
+          <t>135462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>523845</t>
+          <t>522387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>552195</t>
+          <t>550431</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487662</t>
+          <t>486819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515694</t>
+          <t>515581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1020273</t>
+          <t>1018578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1059852</t>
+          <t>1059880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69911</t>
+          <t>68503</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105167</t>
+          <t>105646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83822</t>
+          <t>80044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119584</t>
+          <t>116648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161599</t>
+          <t>160561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213216</t>
+          <t>210585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>562858</t>
+          <t>562379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>598114</t>
+          <t>599522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>540875</t>
+          <t>543811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>576637</t>
+          <t>580415</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1115267</t>
+          <t>1117898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1166884</t>
+          <t>1167922</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111307</t>
+          <t>111618</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154402</t>
+          <t>152696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82721</t>
+          <t>83323</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120379</t>
+          <t>120604</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204517</t>
+          <t>206377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>261660</t>
+          <t>260147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>491646</t>
+          <t>493352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>534741</t>
+          <t>534430</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>526582</t>
+          <t>526357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>564240</t>
+          <t>563638</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1031349</t>
+          <t>1032862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1088492</t>
+          <t>1086632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139370</t>
+          <t>139900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180395</t>
+          <t>184652</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53524</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87611</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>199570</t>
+          <t>200352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>257241</t>
+          <t>256929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>297523</t>
+          <t>293266</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338548</t>
+          <t>338018</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>408129</t>
+          <t>407368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442216</t>
+          <t>442098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>716417</t>
+          <t>716729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>774088</t>
+          <t>773306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>123679</t>
+          <t>125024</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>159711</t>
+          <t>161659</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>44016</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>151316</t>
+          <t>151478</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>196677</t>
+          <t>195831</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174619</t>
+          <t>172671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210651</t>
+          <t>209306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332477</t>
+          <t>333746</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>355938</t>
+          <t>355879</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>515415</t>
+          <t>516261</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>560776</t>
+          <t>560614</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108564</t>
+          <t>107249</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135746</t>
+          <t>135265</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107236</t>
+          <t>108375</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>145487</t>
+          <t>148394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>120387</t>
+          <t>120868</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147569</t>
+          <t>148884</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>384356</t>
+          <t>387236</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>397667</t>
+          <t>397673</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>509530</t>
+          <t>506623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>547781</t>
+          <t>546642</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,45%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>657993</t>
+          <t>652164</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>752729</t>
+          <t>749469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>351550</t>
+          <t>350920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>427302</t>
+          <t>428908</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1025856</t>
+          <t>1030338</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1154919</t>
+          <t>1155140</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2639685</t>
+          <t>2642945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2734421</t>
+          <t>2740250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3111801</t>
+          <t>3110195</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3187553</t>
+          <t>3188183</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5776598</t>
+          <t>5776377</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5905661</t>
+          <t>5901179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31177</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>15484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44159</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -3818,32 +3818,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>392324</t>
+          <t>401328</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376115</t>
+          <t>388302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398132</t>
+          <t>406268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3853,32 +3853,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>292340</t>
+          <t>339768</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279461</t>
+          <t>325575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301265</t>
+          <t>349395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>684664</t>
+          <t>741097</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>666466</t>
+          <t>725485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>695694</t>
+          <t>752358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>310638</t>
+          <t>360048</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>310638</t>
+          <t>360048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310638</t>
+          <t>360048</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>710625</t>
+          <t>767842</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>710625</t>
+          <t>767842</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>710625</t>
+          <t>767842</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>14864</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33672</t>
+          <t>40949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4083,32 +4083,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>34069</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>24076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45273</t>
+          <t>48278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>59802</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>44609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70439</t>
+          <t>79809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -4161,32 +4161,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>402890</t>
+          <t>451156</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389875</t>
+          <t>435941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412463</t>
+          <t>462026</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>480965</t>
+          <t>467014</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466231</t>
+          <t>452805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493509</t>
+          <t>477007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>883855</t>
+          <t>918171</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>864612</t>
+          <t>898164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>899012</t>
+          <t>933364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4391,32 +4391,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>36787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59190</t>
+          <t>67508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4426,32 +4426,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>44501</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63772</t>
+          <t>70812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4461,32 +4461,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>105783</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80650</t>
+          <t>87762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119816</t>
+          <t>127295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>491204</t>
+          <t>570377</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>476984</t>
+          <t>552151</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504629</t>
+          <t>582872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4539,32 +4539,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>490265</t>
+          <t>565638</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>478696</t>
+          <t>551327</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>501047</t>
+          <t>577638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4574,32 +4574,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>981468</t>
+          <t>1136015</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>958825</t>
+          <t>1114503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>997991</t>
+          <t>1154036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078641</t>
+          <t>1241798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078641</t>
+          <t>1241798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078641</t>
+          <t>1241798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>348216</t>
+          <t>114573</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134658</t>
+          <t>95987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>640394</t>
+          <t>138397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>87109</t>
+          <t>92481</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>79877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102912</t>
+          <t>106677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>435326</t>
+          <t>207054</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>215490</t>
+          <t>182650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>894997</t>
+          <t>231193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -4847,32 +4847,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>538567</t>
+          <t>584903</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246389</t>
+          <t>561079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>752125</t>
+          <t>603489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4882,32 +4882,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>624428</t>
+          <t>642997</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608625</t>
+          <t>628801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640216</t>
+          <t>655601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4917,32 +4917,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1162994</t>
+          <t>1227900</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>703323</t>
+          <t>1203761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1382830</t>
+          <t>1252304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -4960,17 +4960,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886783</t>
+          <t>699476</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886783</t>
+          <t>699476</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886783</t>
+          <t>699476</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598320</t>
+          <t>1434954</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598320</t>
+          <t>1434954</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598320</t>
+          <t>1434954</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>157857</t>
+          <t>166184</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>138495</t>
+          <t>144550</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180474</t>
+          <t>187440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73334</t>
+          <t>81780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>108073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>244056</t>
+          <t>260510</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220115</t>
+          <t>234094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269526</t>
+          <t>286549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>402347</t>
+          <t>442081</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>379730</t>
+          <t>420825</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421709</t>
+          <t>463715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>461706</t>
+          <t>514529</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>449465</t>
+          <t>500782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>474571</t>
+          <t>527075</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5260,32 +5260,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>864053</t>
+          <t>956610</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>838583</t>
+          <t>930571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>887994</t>
+          <t>983026</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,77%</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1108109</t>
+          <t>1217120</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1108109</t>
+          <t>1217120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1108109</t>
+          <t>1217120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>155499</t>
+          <t>171602</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>140288</t>
+          <t>154307</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>170158</t>
+          <t>187794</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46015</t>
+          <t>49251</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>40237</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75053</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>201513</t>
+          <t>220853</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102857</t>
+          <t>200765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>263555</t>
+          <t>242314</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>212666</t>
+          <t>235478</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>198007</t>
+          <t>219286</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227877</t>
+          <t>252773</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>562353</t>
+          <t>389915</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>533315</t>
+          <t>379765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>589117</t>
+          <t>398929</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5603,32 +5603,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>775020</t>
+          <t>625393</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>712978</t>
+          <t>603932</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>873676</t>
+          <t>645481</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>117575</t>
+          <t>129568</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104129</t>
+          <t>116771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130017</t>
+          <t>145898</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24674</t>
+          <t>26956</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>135250</t>
+          <t>149203</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119826</t>
+          <t>131591</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>151806</t>
+          <t>166394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>165184</t>
+          <t>180630</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152742</t>
+          <t>164300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>193427</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5911,32 +5911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>408156</t>
+          <t>444974</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>401157</t>
+          <t>437653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>413498</t>
+          <t>450489</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5946,32 +5946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>573340</t>
+          <t>625604</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>556784</t>
+          <t>608413</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>588764</t>
+          <t>643216</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>852438</t>
+          <t>663408</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>641386</t>
+          <t>618433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1477012</t>
+          <t>708368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>338037</t>
+          <t>366543</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>337336</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>377059</t>
+          <t>398317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1190474</t>
+          <t>1029951</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>950224</t>
+          <t>976529</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1829952</t>
+          <t>1084078</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -6219,32 +6219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2605182</t>
+          <t>2865953</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1980608</t>
+          <t>2820993</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2816234</t>
+          <t>2910928</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3320214</t>
+          <t>3364837</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3281192</t>
+          <t>3333063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3382553</t>
+          <t>3394044</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5925397</t>
+          <t>6230789</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5285919</t>
+          <t>6176662</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6165647</t>
+          <t>6284211</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
